--- a/samples/12_spreadsheet.xlsx
+++ b/samples/12_spreadsheet.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>株式会社</t>
   </si>
@@ -22,6 +22,13 @@
   </si>
   <si>
     <t>合計</t>
+  </si>
+  <si>
+    <t>件名</t>
+    <rPh sb="0" eb="2">
+      <t>ケンメイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -76,6 +83,9 @@
       <c r="E1" t="s">
         <v>1</v>
       </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
